--- a/louvain_baseline_experiments/louvain_Baseline_lesmis/louvain_Baseline_lesmis_results.xlsx
+++ b/louvain_baseline_experiments/louvain_Baseline_lesmis/louvain_Baseline_lesmis_results.xlsx
@@ -550,13 +550,13 @@
         <v>0.5658216835217132</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001975599996512756</v>
+        <v>0.001894300000458315</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02588190000096802</v>
+        <v>0.02318560000003345</v>
       </c>
       <c r="P2" t="n">
-        <v>0.07626960000197869</v>
+        <v>0.08534580000014103</v>
       </c>
     </row>
   </sheetData>
